--- a/output/Белавиа статус 21.08.2026.xlsx
+++ b/output/Белавиа статус 21.08.2026.xlsx
@@ -6134,8 +6134,8 @@
       <c r="V18" s="33" t="n">
         <v>46208</v>
       </c>
-      <c r="W18" s="19" t="n">
-        <v/>
+      <c r="W18" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X18" s="19" t="inlineStr">
         <is>
@@ -7160,8 +7160,8 @@
       <c r="V22" s="33" t="n">
         <v>46220</v>
       </c>
-      <c r="W22" s="19" t="n">
-        <v/>
+      <c r="W22" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X22" s="19" t="inlineStr">
         <is>
@@ -7415,8 +7415,8 @@
       <c r="V23" s="30" t="n">
         <v>46228</v>
       </c>
-      <c r="W23" s="27" t="n">
-        <v/>
+      <c r="W23" s="30" t="n">
+        <v>46235</v>
       </c>
       <c r="X23" s="27" t="inlineStr">
         <is>
@@ -7670,8 +7670,8 @@
       <c r="V24" s="33" t="n">
         <v>46233</v>
       </c>
-      <c r="W24" s="19" t="n">
-        <v/>
+      <c r="W24" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X24" s="19" t="inlineStr">
         <is>
@@ -7925,8 +7925,8 @@
       <c r="V25" s="30" t="n">
         <v>46234</v>
       </c>
-      <c r="W25" s="27" t="n">
-        <v/>
+      <c r="W25" s="30" t="n">
+        <v>46235</v>
       </c>
       <c r="X25" s="27" t="inlineStr">
         <is>
@@ -8180,8 +8180,8 @@
       <c r="V26" s="33" t="n">
         <v>46234</v>
       </c>
-      <c r="W26" s="19" t="n">
-        <v/>
+      <c r="W26" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X26" s="19" t="inlineStr">
         <is>
@@ -8435,8 +8435,8 @@
       <c r="V27" s="30" t="n">
         <v>46235</v>
       </c>
-      <c r="W27" s="27" t="n">
-        <v/>
+      <c r="W27" s="30" t="n">
+        <v>46235</v>
       </c>
       <c r="X27" s="27" t="inlineStr">
         <is>
@@ -8690,8 +8690,8 @@
       <c r="V28" s="33" t="n">
         <v>46235</v>
       </c>
-      <c r="W28" s="19" t="n">
-        <v/>
+      <c r="W28" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X28" s="19" t="inlineStr">
         <is>
@@ -8945,8 +8945,8 @@
       <c r="V29" s="30" t="n">
         <v>46235</v>
       </c>
-      <c r="W29" s="27" t="n">
-        <v/>
+      <c r="W29" s="30" t="n">
+        <v>46235</v>
       </c>
       <c r="X29" s="27" t="inlineStr">
         <is>
@@ -9454,8 +9454,8 @@
       <c r="V31" s="30" t="n">
         <v>46239</v>
       </c>
-      <c r="W31" s="27" t="n">
-        <v/>
+      <c r="W31" s="30" t="n">
+        <v>46235</v>
       </c>
       <c r="X31" s="27" t="inlineStr">
         <is>
@@ -9711,8 +9711,8 @@
       <c r="V32" s="33" t="n">
         <v>46239</v>
       </c>
-      <c r="W32" s="19" t="n">
-        <v/>
+      <c r="W32" s="33" t="n">
+        <v>46235</v>
       </c>
       <c r="X32" s="19" t="inlineStr">
         <is>
@@ -9968,8 +9968,8 @@
       <c r="V33" s="35" t="n">
         <v>46239</v>
       </c>
-      <c r="W33" t="n">
-        <v/>
+      <c r="W33" s="35" t="n">
+        <v>46235</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <is>
           <t>DAP MSQ
 Дополнение № 334
-Винт</t>
+предупреждающее освещение</t>
         </is>
       </c>
       <c r="G15" s="27" t="inlineStr">
@@ -13657,7 +13657,7 @@
       </c>
       <c r="K15" s="27" t="inlineStr">
         <is>
-          <t>ASNA2083BG2-10</t>
+          <t>2LA006724-40</t>
         </is>
       </c>
       <c r="L15" s="27" t="n">
@@ -13665,11 +13665,11 @@
       </c>
       <c r="M15" s="27" t="inlineStr">
         <is>
-          <t>SCREW</t>
+          <t>RED WARNING LIGHT</t>
         </is>
       </c>
       <c r="N15" s="29" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="O15" s="27" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
       </c>
       <c r="AA15" s="27" t="inlineStr">
         <is>
-          <t>PROPONENT</t>
+          <t>SATAIR</t>
         </is>
       </c>
       <c r="AB15" s="27" t="n">
@@ -13729,32 +13729,32 @@
       </c>
       <c r="AC15" s="27" t="inlineStr">
         <is>
-          <t>#5853</t>
+          <t>#5854</t>
         </is>
       </c>
       <c r="AD15" s="27" t="n">
         <v/>
       </c>
       <c r="AE15" s="31" t="n">
-        <v>5.2</v>
+        <v>2030</v>
       </c>
       <c r="AF15" s="31" t="n">
-        <v>156</v>
+        <v>4060</v>
       </c>
       <c r="AG15" s="31" t="n">
-        <v>10</v>
+        <v>2700</v>
       </c>
       <c r="AH15" s="31" t="n">
-        <v>300</v>
+        <v>5400</v>
       </c>
       <c r="AI15" s="31" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AJ15" s="31" t="n">
         <v/>
       </c>
       <c r="AK15" s="31" t="n">
-        <v>6.24</v>
+        <v>162.4</v>
       </c>
       <c r="AL15" s="31" t="n">
         <v/>
@@ -13791,7 +13791,7 @@
         <v/>
       </c>
       <c r="AV15" s="31" t="n">
-        <v>300</v>
+        <v>5400</v>
       </c>
       <c r="AW15" s="27" t="n">
         <v/>
@@ -13800,7 +13800,7 @@
         <v/>
       </c>
       <c r="AY15" s="27" t="n">
-        <v>156</v>
+        <v>4060</v>
       </c>
       <c r="AZ15" s="27" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
       </c>
       <c r="BB15" s="27" t="inlineStr">
         <is>
-          <t>21.08 WHS</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC15" s="27" t="n">
@@ -13824,8 +13824,10 @@
       <c r="BE15" s="27" t="n">
         <v/>
       </c>
-      <c r="BF15" s="27" t="n">
-        <v/>
+      <c r="BF15" s="27" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG15" s="27" t="n">
         <v/>
@@ -13877,7 +13879,7 @@
         <is>
           <t>DAP MSQ
 Дополнение № 334
-предупреждающее освещение</t>
+Винт</t>
         </is>
       </c>
       <c r="G16" s="19" t="inlineStr">
@@ -13902,7 +13904,7 @@
       </c>
       <c r="K16" s="19" t="inlineStr">
         <is>
-          <t>2LA006724-40</t>
+          <t>ASNA2083BG2-10</t>
         </is>
       </c>
       <c r="L16" s="19" t="n">
@@ -13910,11 +13912,11 @@
       </c>
       <c r="M16" s="19" t="inlineStr">
         <is>
-          <t>RED WARNING LIGHT</t>
+          <t>SCREW</t>
         </is>
       </c>
       <c r="N16" s="20" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="O16" s="19" t="inlineStr">
         <is>
@@ -13966,7 +13968,7 @@
       </c>
       <c r="AA16" s="19" t="inlineStr">
         <is>
-          <t>SATAIR</t>
+          <t>PROPONENT</t>
         </is>
       </c>
       <c r="AB16" s="19" t="n">
@@ -13974,32 +13976,32 @@
       </c>
       <c r="AC16" s="19" t="inlineStr">
         <is>
-          <t>#5854</t>
+          <t>#5853</t>
         </is>
       </c>
       <c r="AD16" s="19" t="n">
         <v/>
       </c>
       <c r="AE16" s="21" t="n">
-        <v>2030</v>
+        <v>5.2</v>
       </c>
       <c r="AF16" s="21" t="n">
-        <v>4060</v>
+        <v>156</v>
       </c>
       <c r="AG16" s="21" t="n">
-        <v>2700</v>
+        <v>10</v>
       </c>
       <c r="AH16" s="21" t="n">
-        <v>5400</v>
+        <v>300</v>
       </c>
       <c r="AI16" s="21" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AJ16" s="21" t="n">
         <v/>
       </c>
       <c r="AK16" s="21" t="n">
-        <v>162.4</v>
+        <v>6.24</v>
       </c>
       <c r="AL16" s="21" t="n">
         <v/>
@@ -14036,7 +14038,7 @@
         <v/>
       </c>
       <c r="AV16" s="21" t="n">
-        <v>5400</v>
+        <v>300</v>
       </c>
       <c r="AW16" s="19" t="n">
         <v/>
@@ -14045,7 +14047,7 @@
         <v/>
       </c>
       <c r="AY16" s="19" t="n">
-        <v>4060</v>
+        <v>156</v>
       </c>
       <c r="AZ16" s="19" t="inlineStr">
         <is>
@@ -14057,7 +14059,7 @@
       </c>
       <c r="BB16" s="19" t="inlineStr">
         <is>
-          <t>ON THE WAY TO WHS</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC16" s="19" t="n">
@@ -14069,8 +14071,10 @@
       <c r="BE16" s="19" t="n">
         <v/>
       </c>
-      <c r="BF16" s="19" t="n">
-        <v/>
+      <c r="BF16" s="19" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG16" s="19" t="n">
         <v/>
@@ -15828,9 +15832,9 @@
           <t>KDV-3</t>
         </is>
       </c>
-      <c r="E24" s="36" t="inlineStr">
-        <is>
-          <t>1 NOT PAID</t>
+      <c r="E24" s="38" t="inlineStr">
+        <is>
+          <t>2 PAID</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -16002,14 +16006,14 @@
       <c r="AV24" s="21" t="n">
         <v>6200</v>
       </c>
-      <c r="AW24" s="19" t="n">
-        <v/>
+      <c r="AW24" s="34" t="n">
+        <v>46255</v>
       </c>
       <c r="AX24" s="19" t="n">
-        <v/>
+        <v>4000</v>
       </c>
       <c r="AY24" s="19" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="AZ24" s="34" t="n">
         <v>46244</v>
@@ -17490,7 +17494,7 @@
       </c>
       <c r="BB30" s="19" t="inlineStr">
         <is>
-          <t>PAID</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC30" s="19" t="n">
@@ -17502,8 +17506,10 @@
       <c r="BE30" s="19" t="n">
         <v/>
       </c>
-      <c r="BF30" s="19" t="n">
-        <v/>
+      <c r="BF30" s="19" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG30" s="19" t="n">
         <v/>
@@ -18717,7 +18723,7 @@
       </c>
       <c r="BB35" s="27" t="inlineStr">
         <is>
-          <t>UNCONFIRMED YET</t>
+          <t>HA WHS</t>
         </is>
       </c>
       <c r="BC35" s="27" t="n">
@@ -18729,8 +18735,10 @@
       <c r="BE35" s="27" t="n">
         <v/>
       </c>
-      <c r="BF35" s="27" t="n">
-        <v/>
+      <c r="BF35" s="27" t="inlineStr">
+        <is>
+          <t>Др</t>
+        </is>
       </c>
       <c r="BG35" s="27" t="n">
         <v/>
@@ -19689,10 +19697,8 @@
       <c r="BA39" s="27" t="n">
         <v/>
       </c>
-      <c r="BB39" s="27" t="inlineStr">
-        <is>
-          <t>UNCONFIRMED YET</t>
-        </is>
+      <c r="BB39" s="27" t="n">
+        <v/>
       </c>
       <c r="BC39" s="27" t="n">
         <v/>
@@ -19703,8 +19709,10 @@
       <c r="BE39" s="27" t="n">
         <v/>
       </c>
-      <c r="BF39" s="27" t="n">
-        <v/>
+      <c r="BF39" s="27" t="inlineStr">
+        <is>
+          <t>Ф</t>
+        </is>
       </c>
       <c r="BG39" s="27" t="n">
         <v/>
